--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6E62C9-21FF-4C4B-95E9-C9A4A14D7DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D010097-662A-4B32-AEC5-2E955DD39479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Database" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>{name/string/UNIQUE/NOT NULL}</t>
   </si>
@@ -40,27 +40,18 @@
     <t>수확한 쌀을 포대자루에 모았다</t>
   </si>
   <si>
-    <t>0 - 재료</t>
-  </si>
-  <si>
     <t>토마토</t>
   </si>
   <si>
     <t>맛있게 여물은 토마토다</t>
   </si>
   <si>
-    <t>1 - 소모품</t>
-  </si>
-  <si>
     <t>호박</t>
   </si>
   <si>
     <t>속이 꽉찬 호박이다. 할로윈에 쓸만해 보인다</t>
   </si>
   <si>
-    <t>2 - 장비</t>
-  </si>
-  <si>
     <t>딸기</t>
   </si>
   <si>
@@ -121,11 +112,31 @@
     <t>낚시</t>
   </si>
   <si>
-    <t>{ItemType/enum/DEFAULT(0)/CHECK IN(0|1|2)}</t>
+    <t>{id/int/UNIQUE/NOT NULL}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{id/int/UNIQUE/NOT NULL}</t>
+    <t>enum ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{itemType/enum/DEFAULT(0)/CHECK IN(0|1|2)}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -223,7 +234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -245,6 +256,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -581,295 +598,310 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.25" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="2">
+        <v>99</v>
+      </c>
       <c r="E2" s="2">
-        <v>99</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="H2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
+      <c r="D3" s="3">
+        <v>99</v>
       </c>
       <c r="E3" s="3">
-        <v>99</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="H3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2">
+        <v>99</v>
       </c>
       <c r="E4" s="2">
-        <v>99</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="H4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3">
+        <v>99</v>
       </c>
       <c r="E5" s="3">
-        <v>99</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <v>99</v>
       </c>
       <c r="E6" s="2">
-        <v>99</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="6">
+        <v>99</v>
       </c>
       <c r="E7" s="6">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7">
+        <v>99</v>
       </c>
       <c r="E8" s="7">
-        <v>99</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6">
+        <v>99</v>
       </c>
       <c r="E9" s="6">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6">
+        <v>99</v>
       </c>
       <c r="E10" s="6">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="4">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4">
         <v>2</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="4">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4">
         <v>2</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D010097-662A-4B32-AEC5-2E955DD39479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D057BA41-085F-4F1B-AD38-4EAA0928C377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,109 +34,116 @@
     <t>{sellPrice/int/CHECK(VALUE &gt;= 0)}</t>
   </si>
   <si>
-    <t>쌀 한포대</t>
+    <t>토마토</t>
+  </si>
+  <si>
+    <t>맛있게 여물은 토마토다</t>
+  </si>
+  <si>
+    <t>호박</t>
+  </si>
+  <si>
+    <t>속이 꽉찬 호박이다. 할로윈에 쓸만해 보인다</t>
+  </si>
+  <si>
+    <t>딸기</t>
+  </si>
+  <si>
+    <t>빨간 딸기가 맛있어보인다</t>
+  </si>
+  <si>
+    <t>토마토 씨앗</t>
+  </si>
+  <si>
+    <t>호박 씨앗</t>
+  </si>
+  <si>
+    <t>딸기 씨앗</t>
+  </si>
+  <si>
+    <t>지렁이</t>
+  </si>
+  <si>
+    <t>바다에 던져</t>
+  </si>
+  <si>
+    <t>괭이</t>
+  </si>
+  <si>
+    <t>대충</t>
+  </si>
+  <si>
+    <t>물뿌리게</t>
+  </si>
+  <si>
+    <t>아무</t>
+  </si>
+  <si>
+    <t>낫</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>낚시대</t>
+  </si>
+  <si>
+    <t>낚시</t>
+  </si>
+  <si>
+    <t>{id/int/UNIQUE/NOT NULL}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{itemType/enum/DEFAULT(0)/CHECK IN(0|1|2)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볍씨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>수확한 쌀을 포대자루에 모았다</t>
-  </si>
-  <si>
-    <t>토마토</t>
-  </si>
-  <si>
-    <t>맛있게 여물은 토마토다</t>
-  </si>
-  <si>
-    <t>호박</t>
-  </si>
-  <si>
-    <t>속이 꽉찬 호박이다. 할로윈에 쓸만해 보인다</t>
-  </si>
-  <si>
-    <t>딸기</t>
-  </si>
-  <si>
-    <t>빨간 딸기가 맛있어보인다</t>
-  </si>
-  <si>
-    <t>쌀</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 씨앗을 심어 쌀를 수확 할 수 있다.</t>
-  </si>
-  <si>
-    <t>토마토 씨앗</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 씨앗을 심어 토마토을 수확 할 수 있다.</t>
-  </si>
-  <si>
-    <t>호박 씨앗</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 씨앗을 심어 호박을 수확 할 수 있다.</t>
-  </si>
-  <si>
-    <t>딸기 씨앗</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 씨앗을 심어 딸기을 수확 할 수 있다.</t>
-  </si>
-  <si>
-    <t>지렁이</t>
-  </si>
-  <si>
-    <t>바다에 던져</t>
-  </si>
-  <si>
-    <t>괭이</t>
-  </si>
-  <si>
-    <t>대충</t>
-  </si>
-  <si>
-    <t>물뿌리게</t>
-  </si>
-  <si>
-    <t>아무</t>
-  </si>
-  <si>
-    <t>낫</t>
-  </si>
-  <si>
-    <t>설명</t>
-  </si>
-  <si>
-    <t>낚시대</t>
-  </si>
-  <si>
-    <t>낚시</t>
-  </si>
-  <si>
-    <t>{id/int/UNIQUE/NOT NULL}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum ItemType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equipment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{itemType/enum/DEFAULT(0)/CHECK IN(0|1|2)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗을 심어 쌀를 수확 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗을 심어 토마토을 수확 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗을 심어 호박을 수확 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗을 심어 딸기을 수확 할 수 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -234,7 +241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -256,9 +263,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -612,7 +616,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -627,24 +631,24 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2">
         <v>99</v>
@@ -652,23 +656,25 @@
       <c r="E2" s="2">
         <v>0</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="H2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>99</v>
@@ -676,23 +682,25 @@
       <c r="E3" s="3">
         <v>0</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="H3" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2">
         <v>99</v>
@@ -700,23 +708,25 @@
       <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="H4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="10">
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>99</v>
@@ -724,35 +734,39 @@
       <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="A6" s="6">
+        <v>100</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="7">
         <v>99</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2"/>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D7" s="6">
         <v>99</v>
@@ -766,13 +780,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7">
         <v>99</v>
@@ -786,13 +800,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6">
         <v>99</v>
@@ -806,13 +820,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D10" s="6">
         <v>99</v>
@@ -826,13 +840,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -846,13 +860,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <v>11</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -866,13 +880,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <v>12</v>
+        <v>1020</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -886,13 +900,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>1030</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>

--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D057BA41-085F-4F1B-AD38-4EAA0928C377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD843B-72E8-4E62-809E-FDF5D214FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>{name/string/UNIQUE/NOT NULL}</t>
   </si>
@@ -144,6 +144,34 @@
   </si>
   <si>
     <t>씨앗을 심어 딸기을 수확 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anchovy</t>
+  </si>
+  <si>
+    <t>Sea snake</t>
+  </si>
+  <si>
+    <t>Seahorse</t>
+  </si>
+  <si>
+    <t>Frog</t>
+  </si>
+  <si>
+    <t>대충</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무거나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넣으</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시오</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -177,18 +205,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -209,6 +225,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,7 +269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -249,14 +277,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -265,9 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -602,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.625" style="1" bestFit="1" customWidth="1"/>
@@ -615,307 +644,387 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>100</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5">
+        <v>99</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>110</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4">
+        <v>99</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>120</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5">
+        <v>99</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>130</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4">
+        <v>99</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>200</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4">
+        <v>99</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="2">
-        <v>99</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D11" s="9">
+        <v>99</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>1100</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
-        <v>99</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D12" s="8">
+        <v>99</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1200</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2">
-        <v>99</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="D13" s="9">
+        <v>99</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>1300</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="8">
+        <v>99</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2000</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="10">
+        <v>99</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>2100</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="10">
+        <v>99</v>
+      </c>
+      <c r="E16" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>30</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>99</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>100</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="7">
-        <v>99</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>110</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="6">
-        <v>99</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>120</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="7">
-        <v>99</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>130</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="6">
-        <v>99</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>200</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="6">
-        <v>99</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>100</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>1010</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>100</v>
-      </c>
-      <c r="F12" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>1020</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
-        <v>100</v>
-      </c>
-      <c r="F13" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>1030</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>100</v>
-      </c>
-      <c r="F14" s="4">
-        <v>2</v>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>2200</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="10">
+        <v>99</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>2300</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="10">
+        <v>99</v>
+      </c>
+      <c r="E18" s="10">
+        <v>4</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD843B-72E8-4E62-809E-FDF5D214FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB274F4-4D59-4AA2-9CCF-A0BE8B532B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>{name/string/UNIQUE/NOT NULL}</t>
   </si>
@@ -73,9 +73,6 @@
     <t>대충</t>
   </si>
   <si>
-    <t>물뿌리게</t>
-  </si>
-  <si>
     <t>아무</t>
   </si>
   <si>
@@ -172,6 +169,18 @@
   </si>
   <si>
     <t>시오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물뿌리개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대용량 물뿌리개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 많은 물을 담을 수 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.625" style="1" bestFit="1" customWidth="1"/>
@@ -645,7 +654,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -660,13 +669,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -689,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="7">
         <v>0</v>
@@ -700,10 +709,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -715,7 +724,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -723,39 +732,35 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="7">
-        <v>2</v>
-      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -766,61 +771,67 @@
       <c r="F5" s="2">
         <v>2</v>
       </c>
+      <c r="H5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
         <v>100</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="5">
-        <v>99</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1</v>
+      <c r="F6" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
-        <v>110</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="4">
-        <v>99</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
+        <v>100</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5">
+        <v>99</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>120</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5">
-        <v>99</v>
-      </c>
-      <c r="E8" s="5">
+        <v>110</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4">
+        <v>99</v>
+      </c>
+      <c r="E8" s="4">
         <v>0</v>
       </c>
       <c r="F8" s="4">
@@ -829,18 +840,18 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
-        <v>130</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="4">
-        <v>99</v>
-      </c>
-      <c r="E9" s="4">
+        <v>120</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5">
+        <v>99</v>
+      </c>
+      <c r="E9" s="5">
         <v>0</v>
       </c>
       <c r="F9" s="4">
@@ -849,58 +860,58 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
+        <v>130</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4">
+        <v>99</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>200</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4">
-        <v>99</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>1000</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="9">
-        <v>99</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
+      <c r="D11" s="4">
+        <v>99</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>1100</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8">
-        <v>99</v>
-      </c>
-      <c r="E12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9">
+        <v>99</v>
+      </c>
+      <c r="E12" s="9">
         <v>0</v>
       </c>
       <c r="F12" s="9">
@@ -909,18 +920,18 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>1200</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="9">
-        <v>99</v>
-      </c>
-      <c r="E13" s="9">
+        <v>1100</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>99</v>
+      </c>
+      <c r="E13" s="8">
         <v>0</v>
       </c>
       <c r="F13" s="9">
@@ -929,59 +940,59 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
+        <v>1200</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="9">
+        <v>99</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>1300</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="8">
-        <v>99</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>2000</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="10">
-        <v>99</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5">
+      <c r="D15" s="8">
+        <v>99</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" s="10">
         <v>99</v>
       </c>
       <c r="E16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -989,19 +1000,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" s="10">
         <v>99</v>
       </c>
       <c r="E17" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5">
         <v>0</v>
@@ -1009,21 +1020,41 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
+        <v>2200</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="10">
+        <v>99</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>2300</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="10">
-        <v>99</v>
-      </c>
-      <c r="E18" s="10">
+      <c r="B19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="10">
+        <v>99</v>
+      </c>
+      <c r="E19" s="10">
         <v>4</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F19" s="5">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB274F4-4D59-4AA2-9CCF-A0BE8B532B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A31B1A1-2029-4DC6-AC5A-1B09DDF97C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
+    <sheet name="enum ItemType" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -156,22 +157,6 @@
     <t>Frog</t>
   </si>
   <si>
-    <t>대충</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무거나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>넣으</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>물뿌리개</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,6 +166,22 @@
   </si>
   <si>
     <t>더 많은 물을 담을 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입니</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.625" style="1" bestFit="1" customWidth="1"/>
@@ -652,7 +653,7 @@
     <col min="8" max="8" width="15.25" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
@@ -671,14 +672,8 @@
       <c r="F1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -695,21 +690,15 @@
         <v>100</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
@@ -721,24 +710,18 @@
         <v>100</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -747,12 +730,10 @@
         <v>200</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>20</v>
       </c>
@@ -769,16 +750,10 @@
         <v>100</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>30</v>
       </c>
@@ -795,10 +770,10 @@
         <v>100</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>100</v>
       </c>
@@ -818,7 +793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>110</v>
       </c>
@@ -838,7 +813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>120</v>
       </c>
@@ -858,7 +833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>130</v>
       </c>
@@ -878,7 +853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>200</v>
       </c>
@@ -898,7 +873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>1000</v>
       </c>
@@ -915,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1100</v>
       </c>
@@ -935,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1200</v>
       </c>
@@ -955,10 +930,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1300</v>
       </c>
@@ -975,10 +950,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>2000</v>
       </c>
@@ -986,7 +961,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="10">
         <v>99</v>
@@ -995,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1006,7 +981,7 @@
         <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" s="10">
         <v>99</v>
@@ -1015,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1026,7 +1001,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D18" s="10">
         <v>99</v>
@@ -1035,7 +1010,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1046,7 +1021,7 @@
         <v>39</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D19" s="10">
         <v>99</v>
@@ -1055,7 +1030,54 @@
         <v>4</v>
       </c>
       <c r="F19" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24F2156-F927-4594-8663-BE0E26A1014A}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Project/Csv/Item/ItemTable.xlsx
+++ b/Assets/Project/Csv/Item/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A31B1A1-2029-4DC6-AC5A-1B09DDF97C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14C8D45-E0CB-4A38-8DC4-3B8D10A03927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>쌀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수확한 쌀을 포대자루에 모았다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,6 +178,10 @@
   </si>
   <si>
     <t>.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
@@ -718,10 +718,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -781,7 +781,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5">
         <v>99</v>
@@ -801,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4">
         <v>99</v>
@@ -821,7 +821,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5">
         <v>99</v>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="4">
         <v>99</v>
@@ -878,10 +878,10 @@
         <v>1000</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="D12" s="9">
         <v>99</v>
@@ -958,10 +958,10 @@
         <v>2000</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="10">
         <v>99</v>
@@ -978,10 +978,10 @@
         <v>2100</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="10">
         <v>99</v>
@@ -998,10 +998,10 @@
         <v>2200</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="10">
         <v>99</v>
@@ -1018,10 +1018,10 @@
         <v>2300</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" s="10">
         <v>99</v>
